--- a/Outcome/Appendix/figure_data/fig9.xlsx
+++ b/Outcome/Appendix/figure_data/fig9.xlsx
@@ -14411,19 +14411,19 @@
         <v>43831</v>
       </c>
       <c r="B338" t="n">
-        <v>5.56836327056391</v>
+        <v>6.25135948094788</v>
       </c>
       <c r="C338" t="n">
-        <v>0.0790077358284032</v>
+        <v>0.454170338166207</v>
       </c>
       <c r="D338" t="n">
-        <v>0.0385351322999363</v>
+        <v>0.164547698158093</v>
       </c>
       <c r="E338" t="n">
-        <v>56.4424593575199</v>
+        <v>75.4918829271743</v>
       </c>
       <c r="F338" t="n">
-        <v>142.521336180247</v>
+        <v>199.165886900681</v>
       </c>
       <c r="G338" t="s">
         <v>71</v>
@@ -14438,7 +14438,7 @@
         <v>53</v>
       </c>
       <c r="K338" t="n">
-        <v>0.557</v>
+        <v>0.626</v>
       </c>
       <c r="L338" t="s">
         <v>15</v>
@@ -14452,19 +14452,19 @@
         <v>43862</v>
       </c>
       <c r="B339" t="n">
-        <v>1.06834250932295</v>
+        <v>2.11142732668997</v>
       </c>
       <c r="C339" t="n">
-        <v>0.0346119219775067</v>
+        <v>0.173469203548023</v>
       </c>
       <c r="D339" t="n">
-        <v>0.0250346901665305</v>
+        <v>0.0686066585099932</v>
       </c>
       <c r="E339" t="n">
-        <v>22.5261321519616</v>
+        <v>25.9155115235965</v>
       </c>
       <c r="F339" t="n">
-        <v>41.1869069338798</v>
+        <v>68.532729069097</v>
       </c>
       <c r="G339" t="s">
         <v>71</v>
@@ -14473,13 +14473,13 @@
         <v>3</v>
       </c>
       <c r="I339" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="J339" t="s">
         <v>53</v>
       </c>
       <c r="K339" t="n">
-        <v>0.358</v>
+        <v>0.705</v>
       </c>
       <c r="L339" t="s">
         <v>15</v>
@@ -14493,19 +14493,19 @@
         <v>43891</v>
       </c>
       <c r="B340" t="n">
-        <v>3.76147647968004</v>
+        <v>3.5095044974436</v>
       </c>
       <c r="C340" t="n">
-        <v>0.0756745934286073</v>
+        <v>0.424048155069521</v>
       </c>
       <c r="D340" t="n">
-        <v>0.0365784690223072</v>
+        <v>0.148153240585963</v>
       </c>
       <c r="E340" t="n">
-        <v>23.8737262511253</v>
+        <v>23.3919341322693</v>
       </c>
       <c r="F340" t="n">
-        <v>64.1339787133317</v>
+        <v>65.9371833079723</v>
       </c>
       <c r="G340" t="s">
         <v>71</v>
@@ -14520,7 +14520,7 @@
         <v>53</v>
       </c>
       <c r="K340" t="n">
-        <v>0.471</v>
+        <v>0.439</v>
       </c>
       <c r="L340" t="s">
         <v>15</v>
@@ -14534,13 +14534,13 @@
         <v>43922</v>
       </c>
       <c r="B341" t="n">
-        <v>2.21805088566939</v>
+        <v>2.77541913705538</v>
       </c>
       <c r="C341" t="n">
-        <v>0.0124502123552151</v>
+        <v>0.303319360827116</v>
       </c>
       <c r="D341" t="n">
-        <v>0.00472910964327388</v>
+        <v>0.100892297426241</v>
       </c>
       <c r="E341" t="n">
         <v>25.419966274567</v>
@@ -14555,13 +14555,13 @@
         <v>2</v>
       </c>
       <c r="I341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J341" t="s">
         <v>14</v>
       </c>
       <c r="K341" t="n">
-        <v>1.108</v>
+        <v>1.386</v>
       </c>
       <c r="L341" t="s">
         <v>15</v>
@@ -14575,19 +14575,19 @@
         <v>43952</v>
       </c>
       <c r="B342" t="n">
-        <v>3.40004581615025</v>
+        <v>2.80798037644665</v>
       </c>
       <c r="C342" t="n">
-        <v>0.0726124737308183</v>
+        <v>0.277160888917883</v>
       </c>
       <c r="D342" t="n">
-        <v>0.0347951802834315</v>
+        <v>0.0936997251092354</v>
       </c>
       <c r="E342" t="n">
-        <v>25.4391854031768</v>
+        <v>26.161642795898</v>
       </c>
       <c r="F342" t="n">
-        <v>49.338036503476</v>
+        <v>83.2920533554078</v>
       </c>
       <c r="G342" t="s">
         <v>71</v>
@@ -14602,7 +14602,7 @@
         <v>14</v>
       </c>
       <c r="K342" t="n">
-        <v>3.376</v>
+        <v>2.79</v>
       </c>
       <c r="L342" t="s">
         <v>15</v>
@@ -14616,19 +14616,19 @@
         <v>43983</v>
       </c>
       <c r="B343" t="n">
-        <v>3.21113726720175</v>
+        <v>3.2707189880719</v>
       </c>
       <c r="C343" t="n">
-        <v>0.0104581094011479</v>
+        <v>0.320571440758656</v>
       </c>
       <c r="D343" t="n">
-        <v>0.0052095184409126</v>
+        <v>0.099277141650909</v>
       </c>
       <c r="E343" t="n">
-        <v>26.2543348565213</v>
+        <v>26.8694077931572</v>
       </c>
       <c r="F343" t="n">
-        <v>68.4175352796886</v>
+        <v>86.7628199739309</v>
       </c>
       <c r="G343" t="s">
         <v>71</v>
@@ -14643,7 +14643,7 @@
         <v>53</v>
       </c>
       <c r="K343" t="n">
-        <v>0.803</v>
+        <v>0.818</v>
       </c>
       <c r="L343" t="s">
         <v>15</v>
@@ -14657,19 +14657,19 @@
         <v>44013</v>
       </c>
       <c r="B344" t="n">
-        <v>5.57576753402609</v>
+        <v>2.35312527164478</v>
       </c>
       <c r="C344" t="n">
-        <v>0.0290632263879517</v>
+        <v>0.297858732968617</v>
       </c>
       <c r="D344" t="n">
-        <v>0.0147350388177534</v>
+        <v>0.095352126516606</v>
       </c>
       <c r="E344" t="n">
-        <v>46.6944910732437</v>
+        <v>27.5875463347952</v>
       </c>
       <c r="F344" t="n">
-        <v>82.4923440625069</v>
+        <v>90.3342702806335</v>
       </c>
       <c r="G344" t="s">
         <v>71</v>
@@ -14678,13 +14678,13 @@
         <v>2</v>
       </c>
       <c r="I344" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J344" t="s">
         <v>14</v>
       </c>
       <c r="K344" t="n">
-        <v>2.779</v>
+        <v>1.176</v>
       </c>
       <c r="L344" t="s">
         <v>15</v>
@@ -14698,19 +14698,19 @@
         <v>44044</v>
       </c>
       <c r="B345" t="n">
-        <v>5.47351432152032</v>
+        <v>3.16811906800544</v>
       </c>
       <c r="C345" t="n">
-        <v>0.0271150006550495</v>
+        <v>0.290268971329614</v>
       </c>
       <c r="D345" t="n">
-        <v>0.0163428805173707</v>
+        <v>0.0916252847338969</v>
       </c>
       <c r="E345" t="n">
-        <v>46.9500889505306</v>
+        <v>28.316187242018</v>
       </c>
       <c r="F345" t="n">
-        <v>86.6436760126747</v>
+        <v>94.0086002853932</v>
       </c>
       <c r="G345" t="s">
         <v>71</v>
@@ -14719,13 +14719,13 @@
         <v>4</v>
       </c>
       <c r="I345" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J345" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="K345" t="n">
-        <v>1.367</v>
+        <v>0.793</v>
       </c>
       <c r="L345" t="s">
         <v>15</v>
@@ -14739,19 +14739,19 @@
         <v>44075</v>
       </c>
       <c r="B346" t="n">
-        <v>4.75853373286641</v>
+        <v>2.02298731782924</v>
       </c>
       <c r="C346" t="n">
-        <v>0.033081403386759</v>
+        <v>0.0869620598572023</v>
       </c>
       <c r="D346" t="n">
-        <v>0.01096031183604</v>
+        <v>0.0292252696984278</v>
       </c>
       <c r="E346" t="n">
-        <v>28.7286487007791</v>
+        <v>29.055459028013</v>
       </c>
       <c r="F346" t="n">
-        <v>75.2499407244571</v>
+        <v>97.7880419033661</v>
       </c>
       <c r="G346" t="s">
         <v>71</v>
@@ -14760,13 +14760,13 @@
         <v>5</v>
       </c>
       <c r="I346" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="J346" t="s">
         <v>53</v>
       </c>
       <c r="K346" t="n">
-        <v>0.952</v>
+        <v>0.406</v>
       </c>
       <c r="L346" t="s">
         <v>15</v>
@@ -14780,19 +14780,19 @@
         <v>44105</v>
       </c>
       <c r="B347" t="n">
-        <v>5.35054749251457</v>
+        <v>2.84158633714708</v>
       </c>
       <c r="C347" t="n">
-        <v>0.0230709589281343</v>
+        <v>0.279896135182077</v>
       </c>
       <c r="D347" t="n">
-        <v>0.0132153829841217</v>
+        <v>0.0847167575749647</v>
       </c>
       <c r="E347" t="n">
-        <v>38.3877405618229</v>
+        <v>29.8054900058925</v>
       </c>
       <c r="F347" t="n">
-        <v>90.6382284784762</v>
+        <v>101.674863570672</v>
       </c>
       <c r="G347" t="s">
         <v>71</v>
@@ -14801,13 +14801,13 @@
         <v>4</v>
       </c>
       <c r="I347" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J347" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="K347" t="n">
-        <v>1.337</v>
+        <v>0.711</v>
       </c>
       <c r="L347" t="s">
         <v>15</v>
@@ -14821,19 +14821,19 @@
         <v>44136</v>
       </c>
       <c r="B348" t="n">
-        <v>6.68849552326736</v>
+        <v>1.55694332693314</v>
       </c>
       <c r="C348" t="n">
-        <v>0.0354889051189606</v>
+        <v>0.0513160126864068</v>
       </c>
       <c r="D348" t="n">
-        <v>0.0134938738707895</v>
+        <v>0.0195443897684454</v>
       </c>
       <c r="E348" t="n">
-        <v>35.0653422785116</v>
+        <v>30.5664083859404</v>
       </c>
       <c r="F348" t="n">
-        <v>80.7503043823891</v>
+        <v>105.671370854394</v>
       </c>
       <c r="G348" t="s">
         <v>71</v>
@@ -14842,13 +14842,13 @@
         <v>2</v>
       </c>
       <c r="I348" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J348" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="K348" t="n">
-        <v>3.333</v>
+        <v>0.78</v>
       </c>
       <c r="L348" t="s">
         <v>15</v>
@@ -14862,19 +14862,19 @@
         <v>44166</v>
       </c>
       <c r="B349" t="n">
-        <v>4.89348907221805</v>
+        <v>2.57526507861285</v>
       </c>
       <c r="C349" t="n">
-        <v>0.0332471028691264</v>
+        <v>0.234359639380836</v>
       </c>
       <c r="D349" t="n">
-        <v>0.00981667666832313</v>
+        <v>0.0784621248039357</v>
       </c>
       <c r="E349" t="n">
-        <v>31.2003357192235</v>
+        <v>31.3383423634748</v>
       </c>
       <c r="F349" t="n">
-        <v>84.6378576841022</v>
+        <v>109.779907058446</v>
       </c>
       <c r="G349" t="s">
         <v>71</v>
@@ -14883,13 +14883,13 @@
         <v>1</v>
       </c>
       <c r="I349" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J349" t="s">
         <v>14</v>
       </c>
       <c r="K349" t="n">
-        <v>4.855</v>
+        <v>2.56</v>
       </c>
       <c r="L349" t="s">
         <v>15</v>
@@ -14903,19 +14903,19 @@
         <v>44197</v>
       </c>
       <c r="B350" t="n">
-        <v>5.03937075394806</v>
+        <v>1.32996308569854</v>
       </c>
       <c r="C350" t="n">
-        <v>0.0373077466465104</v>
+        <v>0.0348181734031333</v>
       </c>
       <c r="D350" t="n">
-        <v>0.0148298005435943</v>
+        <v>0.0134114264470131</v>
       </c>
       <c r="E350" t="n">
-        <v>32.0253351725353</v>
+        <v>32.1214201984579</v>
       </c>
       <c r="F350" t="n">
-        <v>98.5836464063149</v>
+        <v>114.002853826662</v>
       </c>
       <c r="G350" t="s">
         <v>71</v>
@@ -14924,13 +14924,13 @@
         <v>2</v>
       </c>
       <c r="I350" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="J350" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="K350" t="n">
-        <v>2.512</v>
+        <v>0.667</v>
       </c>
       <c r="L350" t="s">
         <v>15</v>
@@ -14944,19 +14944,19 @@
         <v>44228</v>
       </c>
       <c r="B351" t="n">
-        <v>4.73682260715059</v>
+        <v>2.20200266938457</v>
       </c>
       <c r="C351" t="n">
-        <v>0.0494249306158524</v>
+        <v>0.234031850708107</v>
       </c>
       <c r="D351" t="n">
-        <v>0.0173407817045998</v>
+        <v>0.0727849688791691</v>
       </c>
       <c r="E351" t="n">
-        <v>32.8512042190424</v>
+        <v>32.9157702878273</v>
       </c>
       <c r="F351" t="n">
-        <v>94.7721503573001</v>
+        <v>118.342631744251</v>
       </c>
       <c r="G351" t="s">
         <v>71</v>
@@ -14965,13 +14965,13 @@
         <v>3</v>
       </c>
       <c r="I351" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="J351" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="K351" t="n">
-        <v>1.577</v>
+        <v>0.735</v>
       </c>
       <c r="L351" t="s">
         <v>15</v>
@@ -14985,19 +14985,19 @@
         <v>44256</v>
       </c>
       <c r="B352" t="n">
-        <v>4.58825464270587</v>
+        <v>1.56358551194237</v>
       </c>
       <c r="C352" t="n">
-        <v>0.0307669665357616</v>
+        <v>0.0473611284058548</v>
       </c>
       <c r="D352" t="n">
-        <v>0.012829804503463</v>
+        <v>0.02092014457375</v>
       </c>
       <c r="E352" t="n">
-        <v>33.6781152089358</v>
+        <v>33.7215212313925</v>
       </c>
       <c r="F352" t="n">
-        <v>96.0080944336119</v>
+        <v>122.801700938634</v>
       </c>
       <c r="G352" t="s">
         <v>71</v>
@@ -15006,13 +15006,13 @@
         <v>6</v>
       </c>
       <c r="I352" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="J352" t="s">
         <v>53</v>
       </c>
       <c r="K352" t="n">
-        <v>0.765</v>
+        <v>0.262</v>
       </c>
       <c r="L352" t="s">
         <v>15</v>
@@ -15026,19 +15026,19 @@
         <v>44287</v>
       </c>
       <c r="B353" t="n">
-        <v>4.03387286412883</v>
+        <v>2.71090612649237</v>
       </c>
       <c r="C353" t="n">
-        <v>0.0310274957401944</v>
+        <v>0.162640306269854</v>
       </c>
       <c r="D353" t="n">
-        <v>0.010539133645178</v>
+        <v>0.0655781608080556</v>
       </c>
       <c r="E353" t="n">
-        <v>34.5062222753635</v>
+        <v>34.5388018920301</v>
       </c>
       <c r="F353" t="n">
-        <v>107.603357108028</v>
+        <v>127.382561680542</v>
       </c>
       <c r="G353" t="s">
         <v>71</v>
@@ -15047,13 +15047,13 @@
         <v>5</v>
       </c>
       <c r="I353" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J353" t="s">
         <v>53</v>
       </c>
       <c r="K353" t="n">
-        <v>0.807</v>
+        <v>0.543</v>
       </c>
       <c r="L353" t="s">
         <v>15</v>
@@ -15067,19 +15067,19 @@
         <v>44317</v>
       </c>
       <c r="B354" t="n">
-        <v>4.53543072520112</v>
+        <v>1.46975268365974</v>
       </c>
       <c r="C354" t="n">
-        <v>0.0342145376916424</v>
+        <v>0.0553199434733969</v>
       </c>
       <c r="D354" t="n">
-        <v>0.0108505957210481</v>
+        <v>0.0268298658838945</v>
       </c>
       <c r="E354" t="n">
-        <v>35.335667007529</v>
+        <v>35.3677414508137</v>
       </c>
       <c r="F354" t="n">
-        <v>108.242016227613</v>
+        <v>132.087754986133</v>
       </c>
       <c r="G354" t="s">
         <v>71</v>
@@ -15088,13 +15088,13 @@
         <v>1</v>
       </c>
       <c r="I354" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J354" t="s">
         <v>14</v>
       </c>
       <c r="K354" t="n">
-        <v>4.5</v>
+        <v>1.465</v>
       </c>
       <c r="L354" t="s">
         <v>15</v>
@@ -15108,19 +15108,19 @@
         <v>44348</v>
       </c>
       <c r="B355" t="n">
-        <v>4.74851979406036</v>
+        <v>2.71013522774545</v>
       </c>
       <c r="C355" t="n">
-        <v>0.0214833605806014</v>
+        <v>0.117731805302578</v>
       </c>
       <c r="D355" t="n">
-        <v>0.00795389143268031</v>
+        <v>0.0364300369926969</v>
       </c>
       <c r="E355" t="n">
-        <v>36.1665788660949</v>
+        <v>36.2084694576365</v>
       </c>
       <c r="F355" t="n">
-        <v>108.850867423466</v>
+        <v>136.919863220809</v>
       </c>
       <c r="G355" t="s">
         <v>71</v>
@@ -15129,13 +15129,13 @@
         <v>4</v>
       </c>
       <c r="I355" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J355" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="K355" t="n">
-        <v>1.187</v>
+        <v>0.678</v>
       </c>
       <c r="L355" t="s">
         <v>15</v>
@@ -15149,19 +15149,19 @@
         <v>44378</v>
       </c>
       <c r="B356" t="n">
-        <v>4.62704376820772</v>
+        <v>1.95197393742874</v>
       </c>
       <c r="C356" t="n">
-        <v>0.0232617942306044</v>
+        <v>0.105889547849657</v>
       </c>
       <c r="D356" t="n">
-        <v>0.0098373682363552</v>
+        <v>0.0426556049675676</v>
       </c>
       <c r="E356" t="n">
-        <v>36.9990767996497</v>
+        <v>37.0611158778131</v>
       </c>
       <c r="F356" t="n">
-        <v>118.175181863592</v>
+        <v>141.881510705334</v>
       </c>
       <c r="G356" t="s">
         <v>71</v>
@@ -15170,13 +15170,13 @@
         <v>3</v>
       </c>
       <c r="I356" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="J356" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="K356" t="n">
-        <v>1.541</v>
+        <v>0.652</v>
       </c>
       <c r="L356" t="s">
         <v>15</v>
@@ -15190,19 +15190,19 @@
         <v>44409</v>
       </c>
       <c r="B357" t="n">
-        <v>4.60404696605279</v>
+        <v>2.28910124267079</v>
       </c>
       <c r="C357" t="n">
-        <v>0.0209930502538232</v>
+        <v>0.0931332972542656</v>
       </c>
       <c r="D357" t="n">
-        <v>0.00715216785523019</v>
+        <v>0.0266324612941225</v>
       </c>
       <c r="E357" t="n">
-        <v>37.8332702884347</v>
+        <v>37.9258111350872</v>
       </c>
       <c r="F357" t="n">
-        <v>121.691447397971</v>
+        <v>146.975364324767</v>
       </c>
       <c r="G357" t="s">
         <v>71</v>
@@ -15211,13 +15211,13 @@
         <v>2</v>
       </c>
       <c r="I357" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J357" t="s">
         <v>14</v>
       </c>
       <c r="K357" t="n">
-        <v>2.296</v>
+        <v>1.144</v>
       </c>
       <c r="L357" t="s">
         <v>15</v>
@@ -15231,19 +15231,19 @@
         <v>44440</v>
       </c>
       <c r="B358" t="n">
-        <v>4.84818487478048</v>
+        <v>1.976892008557</v>
       </c>
       <c r="C358" t="n">
-        <v>0.0265402725900248</v>
+        <v>0.114693950951088</v>
       </c>
       <c r="D358" t="n">
-        <v>0.00932010980024402</v>
+        <v>0.0565921866525776</v>
       </c>
       <c r="E358" t="n">
-        <v>38.6692603523758</v>
+        <v>38.8026861514224</v>
       </c>
       <c r="F358" t="n">
-        <v>122.83405520058</v>
+        <v>152.204134140696</v>
       </c>
       <c r="G358" t="s">
         <v>71</v>
@@ -15252,13 +15252,13 @@
         <v>1</v>
       </c>
       <c r="I358" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J358" t="s">
         <v>14</v>
       </c>
       <c r="K358" t="n">
-        <v>4.81</v>
+        <v>1.967</v>
       </c>
       <c r="L358" t="s">
         <v>15</v>
@@ -15272,19 +15272,19 @@
         <v>44470</v>
       </c>
       <c r="B359" t="n">
-        <v>4.59603757609496</v>
+        <v>2.74747972108207</v>
       </c>
       <c r="C359" t="n">
-        <v>0.023452377383538</v>
+        <v>0.124118072311289</v>
       </c>
       <c r="D359" t="n">
-        <v>0.00892625424559325</v>
+        <v>0.0437580796917787</v>
       </c>
       <c r="E359" t="n">
-        <v>39.5071404025647</v>
+        <v>39.6918723839059</v>
       </c>
       <c r="F359" t="n">
-        <v>130.400653761745</v>
+        <v>157.570574007182</v>
       </c>
       <c r="G359" t="s">
         <v>71</v>
@@ -15293,13 +15293,13 @@
         <v>1</v>
       </c>
       <c r="I359" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J359" t="s">
         <v>14</v>
       </c>
       <c r="K359" t="n">
-        <v>4.56</v>
+        <v>2.73</v>
       </c>
       <c r="L359" t="s">
         <v>15</v>
@@ -15313,19 +15313,19 @@
         <v>44501</v>
       </c>
       <c r="B360" t="n">
-        <v>4.1247601303152</v>
+        <v>1.93171130807709</v>
       </c>
       <c r="C360" t="n">
-        <v>0.0274210452426564</v>
+        <v>0.110598341451956</v>
       </c>
       <c r="D360" t="n">
-        <v>0.00861457699499174</v>
+        <v>0.0503682883066684</v>
       </c>
       <c r="E360" t="n">
-        <v>40.3469969953386</v>
+        <v>40.5935018590583</v>
       </c>
       <c r="F360" t="n">
-        <v>135.594218870375</v>
+        <v>163.077482190791</v>
       </c>
       <c r="G360" t="s">
         <v>71</v>
@@ -15334,13 +15334,13 @@
         <v>2</v>
       </c>
       <c r="I360" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J360" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="K360" t="n">
-        <v>2.057</v>
+        <v>0.966</v>
       </c>
       <c r="L360" t="s">
         <v>15</v>
@@ -15354,19 +15354,19 @@
         <v>44531</v>
       </c>
       <c r="B361" t="n">
-        <v>4.88311653236559</v>
+        <v>2.41019494918812</v>
       </c>
       <c r="C361" t="n">
-        <v>0.0278625940239522</v>
+        <v>0.112757574346345</v>
       </c>
       <c r="D361" t="n">
-        <v>0.00920057465923425</v>
+        <v>0.044256076116868</v>
       </c>
       <c r="E361" t="n">
-        <v>41.1889104930536</v>
+        <v>41.6184294676252</v>
       </c>
       <c r="F361" t="n">
-        <v>137.798336302233</v>
+        <v>168.727701995071</v>
       </c>
       <c r="G361" t="s">
         <v>71</v>
@@ -15375,13 +15375,13 @@
         <v>3</v>
       </c>
       <c r="I361" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="J361" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="K361" t="n">
-        <v>1.626</v>
+        <v>0.804</v>
       </c>
       <c r="L361" t="s">
         <v>15</v>
@@ -15395,19 +15395,19 @@
         <v>44562</v>
       </c>
       <c r="B362" t="n">
-        <v>4.3990580944791</v>
+        <v>1.73449173937269</v>
       </c>
       <c r="C362" t="n">
-        <v>0.0280930449815559</v>
+        <v>0.0992461894323059</v>
       </c>
       <c r="D362" t="n">
-        <v>0.00884349425319387</v>
+        <v>0.049354580046809</v>
       </c>
       <c r="E362" t="n">
-        <v>42.032955647675</v>
+        <v>42.6992332654454</v>
       </c>
       <c r="F362" t="n">
-        <v>144.234753016366</v>
+        <v>174.524122389755</v>
       </c>
       <c r="G362" t="s">
         <v>71</v>
@@ -15416,13 +15416,13 @@
         <v>6</v>
       </c>
       <c r="I362" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="J362" t="s">
         <v>53</v>
       </c>
       <c r="K362" t="n">
-        <v>0.734</v>
+        <v>0.29</v>
       </c>
       <c r="L362" t="s">
         <v>15</v>
@@ -15436,19 +15436,19 @@
         <v>44593</v>
       </c>
       <c r="B363" t="n">
-        <v>4.62213310316442</v>
+        <v>2.09349535047082</v>
       </c>
       <c r="C363" t="n">
-        <v>0.0294395886491356</v>
+        <v>0.139694120963703</v>
       </c>
       <c r="D363" t="n">
-        <v>0.011287277760607</v>
+        <v>0.0477285981404548</v>
       </c>
       <c r="E363" t="n">
-        <v>42.8792021170852</v>
+        <v>43.7972445529839</v>
       </c>
       <c r="F363" t="n">
-        <v>150.321255667525</v>
+        <v>180.469678645001</v>
       </c>
       <c r="G363" t="s">
         <v>71</v>
@@ -15457,13 +15457,13 @@
         <v>2</v>
       </c>
       <c r="I363" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J363" t="s">
         <v>14</v>
       </c>
       <c r="K363" t="n">
-        <v>2.305</v>
+        <v>1.047</v>
       </c>
       <c r="L363" t="s">
         <v>15</v>
@@ -15477,19 +15477,19 @@
         <v>44621</v>
       </c>
       <c r="B364" t="n">
-        <v>4.60492138091869</v>
+        <v>1.67215366365178</v>
       </c>
       <c r="C364" t="n">
-        <v>0.034823517877537</v>
+        <v>0.0913604930729469</v>
       </c>
       <c r="D364" t="n">
-        <v>0.00960066036464852</v>
+        <v>0.0373174604537924</v>
       </c>
       <c r="E364" t="n">
-        <v>43.7277149234532</v>
+        <v>44.9126713622174</v>
       </c>
       <c r="F364" t="n">
-        <v>153.717685506952</v>
+        <v>186.567352970901</v>
       </c>
       <c r="G364" t="s">
         <v>71</v>
@@ -15498,13 +15498,13 @@
         <v>4</v>
       </c>
       <c r="I364" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J364" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="K364" t="n">
-        <v>1.151</v>
+        <v>0.419</v>
       </c>
       <c r="L364" t="s">
         <v>15</v>
@@ -15518,19 +15518,19 @@
         <v>44652</v>
       </c>
       <c r="B365" t="n">
-        <v>4.47762106435907</v>
+        <v>2.59599784778565</v>
       </c>
       <c r="C365" t="n">
-        <v>0.0334074725356675</v>
+        <v>0.134869150412994</v>
       </c>
       <c r="D365" t="n">
-        <v>0.0120307045621047</v>
+        <v>0.0446714912551257</v>
       </c>
       <c r="E365" t="n">
-        <v>44.5785548612703</v>
+        <v>46.0457229020694</v>
       </c>
       <c r="F365" t="n">
-        <v>159.598529305809</v>
+        <v>192.820175162518</v>
       </c>
       <c r="G365" t="s">
         <v>71</v>
@@ -15539,13 +15539,13 @@
         <v>1</v>
       </c>
       <c r="I365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J365" t="s">
         <v>14</v>
       </c>
       <c r="K365" t="n">
-        <v>4.443</v>
+        <v>2.58</v>
       </c>
       <c r="L365" t="s">
         <v>15</v>
@@ -15559,19 +15559,19 @@
         <v>44682</v>
       </c>
       <c r="B366" t="n">
-        <v>4.5526589984355</v>
+        <v>1.95563575668386</v>
       </c>
       <c r="C366" t="n">
-        <v>0.0281966361766095</v>
+        <v>0.101600390828041</v>
       </c>
       <c r="D366" t="n">
-        <v>0.00835175473820886</v>
+        <v>0.0432340103526227</v>
       </c>
       <c r="E366" t="n">
-        <v>45.4317788615849</v>
+        <v>47.1966096112063</v>
       </c>
       <c r="F366" t="n">
-        <v>166.139111810876</v>
+        <v>199.78189233578</v>
       </c>
       <c r="G366" t="s">
         <v>71</v>
@@ -15580,13 +15580,13 @@
         <v>4</v>
       </c>
       <c r="I366" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J366" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="K366" t="n">
-        <v>1.138</v>
+        <v>0.49</v>
       </c>
       <c r="L366" t="s">
         <v>15</v>
@@ -15600,19 +15600,19 @@
         <v>44713</v>
       </c>
       <c r="B367" t="n">
-        <v>4.54906456104381</v>
+        <v>2.48562591701092</v>
       </c>
       <c r="C367" t="n">
-        <v>0.0261520673887084</v>
+        <v>0.135644833532041</v>
       </c>
       <c r="D367" t="n">
-        <v>0.00871570107144216</v>
+        <v>0.0418533191716252</v>
       </c>
       <c r="E367" t="n">
-        <v>46.2874403179729</v>
+        <v>48.3655432073072</v>
       </c>
       <c r="F367" t="n">
-        <v>170.652824271813</v>
+        <v>207.398717866872</v>
       </c>
       <c r="G367" t="s">
         <v>71</v>
@@ -15621,13 +15621,13 @@
         <v>3</v>
       </c>
       <c r="I367" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="J367" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="K367" t="n">
-        <v>1.515</v>
+        <v>0.829</v>
       </c>
       <c r="L367" t="s">
         <v>15</v>
@@ -15641,19 +15641,19 @@
         <v>44743</v>
       </c>
       <c r="B368" t="n">
-        <v>4.61039790358859</v>
+        <v>1.96564782678572</v>
       </c>
       <c r="C368" t="n">
-        <v>0.0245410498362438</v>
+        <v>0.124701900676866</v>
       </c>
       <c r="D368" t="n">
-        <v>0.00946914834474658</v>
+        <v>0.0405266881623213</v>
       </c>
       <c r="E368" t="n">
-        <v>47.1455893789869</v>
+        <v>49.5527367331774</v>
       </c>
       <c r="F368" t="n">
-        <v>176.429824432968</v>
+        <v>215.234914228426</v>
       </c>
       <c r="G368" t="s">
         <v>71</v>
@@ -15662,13 +15662,13 @@
         <v>9</v>
       </c>
       <c r="I368" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="J368" t="s">
         <v>53</v>
       </c>
       <c r="K368" t="n">
-        <v>0.513</v>
+        <v>0.219</v>
       </c>
       <c r="L368" t="s">
         <v>15</v>
@@ -15682,19 +15682,19 @@
         <v>44774</v>
       </c>
       <c r="B369" t="n">
-        <v>4.58606420205791</v>
+        <v>2.42839404899964</v>
       </c>
       <c r="C369" t="n">
-        <v>0.0243327762275618</v>
+        <v>0.135828541904854</v>
       </c>
       <c r="D369" t="n">
-        <v>0.00909783590977383</v>
+        <v>0.039251545151455</v>
       </c>
       <c r="E369" t="n">
-        <v>48.0062732111485</v>
+        <v>50.7584046000355</v>
       </c>
       <c r="F369" t="n">
-        <v>183.230807582198</v>
+        <v>223.295417450584</v>
       </c>
       <c r="G369" t="s">
         <v>71</v>
@@ -15703,13 +15703,13 @@
         <v>7</v>
       </c>
       <c r="I369" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="J369" t="s">
         <v>53</v>
       </c>
       <c r="K369" t="n">
-        <v>0.656</v>
+        <v>0.348</v>
       </c>
       <c r="L369" t="s">
         <v>15</v>
@@ -15723,19 +15723,19 @@
         <v>44805</v>
       </c>
       <c r="B370" t="n">
-        <v>4.66667831963201</v>
+        <v>1.78901327916856</v>
       </c>
       <c r="C370" t="n">
-        <v>0.0211688275359364</v>
+        <v>0.118885304640667</v>
       </c>
       <c r="D370" t="n">
-        <v>0.00821178022149809</v>
+        <v>0.0380254646369259</v>
       </c>
       <c r="E370" t="n">
-        <v>48.8695362359817</v>
+        <v>51.982762628261</v>
       </c>
       <c r="F370" t="n">
-        <v>188.711079152616</v>
+        <v>231.585252687965</v>
       </c>
       <c r="G370" t="s">
         <v>71</v>
@@ -15744,13 +15744,13 @@
         <v>0</v>
       </c>
       <c r="I370" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J370" t="s">
         <v>14</v>
       </c>
       <c r="K370" t="n">
-        <v>467.668</v>
+        <v>179.901</v>
       </c>
       <c r="L370" t="s">
         <v>72</v>
@@ -15764,19 +15764,19 @@
         <v>44835</v>
       </c>
       <c r="B371" t="n">
-        <v>4.64487539132717</v>
+        <v>2.35364126001695</v>
       </c>
       <c r="C371" t="n">
-        <v>0.0201357055776094</v>
+        <v>0.14528816089829</v>
       </c>
       <c r="D371" t="n">
-        <v>0.00783691473583483</v>
+        <v>0.036846157927115</v>
       </c>
       <c r="E371" t="n">
-        <v>49.7354203441117</v>
+        <v>53.2260280858621</v>
       </c>
       <c r="F371" t="n">
-        <v>194.701889550815</v>
+        <v>240.109535588598</v>
       </c>
       <c r="G371" t="s">
         <v>71</v>
@@ -15785,13 +15785,13 @@
         <v>2</v>
       </c>
       <c r="I371" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J371" t="s">
         <v>14</v>
       </c>
       <c r="K371" t="n">
-        <v>2.316</v>
+        <v>1.176</v>
       </c>
       <c r="L371" t="s">
         <v>15</v>
@@ -15805,19 +15805,19 @@
         <v>44866</v>
       </c>
       <c r="B372" t="n">
-        <v>4.57794971576981</v>
+        <v>1.72595728625882</v>
       </c>
       <c r="C372" t="n">
-        <v>0.0222154436960487</v>
+        <v>0.114310372799973</v>
       </c>
       <c r="D372" t="n">
-        <v>0.00813074905723304</v>
+        <v>0.0357114640488407</v>
       </c>
       <c r="E372" t="n">
-        <v>50.6039650890439</v>
+        <v>54.4884197248891</v>
       </c>
       <c r="F372" t="n">
-        <v>201.722620292553</v>
+        <v>248.873473678148</v>
       </c>
       <c r="G372" t="s">
         <v>71</v>
@@ -15826,13 +15826,13 @@
         <v>3</v>
       </c>
       <c r="I372" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="J372" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="K372" t="n">
-        <v>1.524</v>
+        <v>0.577</v>
       </c>
       <c r="L372" t="s">
         <v>15</v>
@@ -15846,19 +15846,19 @@
         <v>44896</v>
       </c>
       <c r="B373" t="n">
-        <v>4.72249807021222</v>
+        <v>2.43417602347705</v>
       </c>
       <c r="C373" t="n">
-        <v>0.0225308424271074</v>
+        <v>0.144373229974249</v>
       </c>
       <c r="D373" t="n">
-        <v>0.00814782160695889</v>
+        <v>0.0346193413555652</v>
       </c>
       <c r="E373" t="n">
-        <v>51.4752078629001</v>
+        <v>55.7701578159976</v>
       </c>
       <c r="F373" t="n">
-        <v>208.018086463898</v>
+        <v>257.882367759848</v>
       </c>
       <c r="G373" t="s">
         <v>71</v>
@@ -15867,13 +15867,13 @@
         <v>2</v>
       </c>
       <c r="I373" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J373" t="s">
         <v>14</v>
       </c>
       <c r="K373" t="n">
-        <v>2.354</v>
+        <v>1.216</v>
       </c>
       <c r="L373" t="s">
         <v>15</v>
@@ -15887,19 +15887,19 @@
         <v>44927</v>
       </c>
       <c r="B374" t="n">
-        <v>4.60057593014048</v>
+        <v>1.83020977210463</v>
       </c>
       <c r="C374" t="n">
-        <v>0.0210320778214845</v>
+        <v>0.117656381702524</v>
       </c>
       <c r="D374" t="n">
-        <v>0.00817617500161078</v>
+        <v>0.0335678597743147</v>
       </c>
       <c r="E374" t="n">
-        <v>52.3491840560926</v>
+        <v>57.0714641813421</v>
       </c>
       <c r="F374" t="n">
-        <v>214.425608687819</v>
+        <v>267.14161333049</v>
       </c>
       <c r="G374" t="s">
         <v>71</v>
@@ -15908,13 +15908,13 @@
         <v>11</v>
       </c>
       <c r="I374" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="J374" t="s">
         <v>53</v>
       </c>
       <c r="K374" t="n">
-        <v>0.419</v>
+        <v>0.167</v>
       </c>
       <c r="L374" t="s">
         <v>15</v>
@@ -15928,19 +15928,19 @@
         <v>44958</v>
       </c>
       <c r="B375" t="n">
-        <v>4.66781094599089</v>
+        <v>2.51253625879777</v>
       </c>
       <c r="C375" t="n">
-        <v>0.0249572015098872</v>
+        <v>0.134316264629236</v>
       </c>
       <c r="D375" t="n">
-        <v>0.0086258033779284</v>
+        <v>0.0325551936358638</v>
       </c>
       <c r="E375" t="n">
-        <v>53.2259272026667</v>
+        <v>58.3925622259614</v>
       </c>
       <c r="F375" t="n">
-        <v>221.708011385791</v>
+        <v>276.656702012848</v>
       </c>
       <c r="G375" t="s">
         <v>71</v>
@@ -15949,13 +15949,13 @@
         <v>6</v>
       </c>
       <c r="I375" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="J375" t="s">
         <v>53</v>
       </c>
       <c r="K375" t="n">
-        <v>0.778</v>
+        <v>0.42</v>
       </c>
       <c r="L375" t="s">
         <v>15</v>
@@ -15969,19 +15969,19 @@
         <v>44986</v>
       </c>
       <c r="B376" t="n">
-        <v>4.69625241927719</v>
+        <v>1.84116075256485</v>
       </c>
       <c r="C376" t="n">
-        <v>0.026725534172966</v>
+        <v>0.120243706176178</v>
       </c>
       <c r="D376" t="n">
-        <v>0.00947676830907041</v>
+        <v>0.0315796150381476</v>
       </c>
       <c r="E376" t="n">
-        <v>54.105469112831</v>
+        <v>59.7336769678005</v>
       </c>
       <c r="F376" t="n">
-        <v>228.701348004303</v>
+        <v>286.433223004854</v>
       </c>
       <c r="G376" t="s">
         <v>71</v>
@@ -15990,13 +15990,13 @@
         <v>7</v>
       </c>
       <c r="I376" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="J376" t="s">
         <v>53</v>
       </c>
       <c r="K376" t="n">
-        <v>0.671</v>
+        <v>0.264</v>
       </c>
       <c r="L376" t="s">
         <v>15</v>
@@ -16010,19 +16010,19 @@
         <v>45017</v>
       </c>
       <c r="B377" t="n">
-        <v>4.64708158652965</v>
+        <v>2.49878496440025</v>
       </c>
       <c r="C377" t="n">
-        <v>0.0290791258057125</v>
+        <v>0.142119852229573</v>
       </c>
       <c r="D377" t="n">
-        <v>0.00969932608031585</v>
+        <v>0.0306394876976929</v>
       </c>
       <c r="E377" t="n">
-        <v>54.9878399940061</v>
+        <v>61.0950350664979</v>
       </c>
       <c r="F377" t="n">
-        <v>235.644175775225</v>
+        <v>296.476864545863</v>
       </c>
       <c r="G377" t="s">
         <v>71</v>
@@ -16031,13 +16031,13 @@
         <v>0</v>
       </c>
       <c r="I377" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J377" t="s">
         <v>14</v>
       </c>
       <c r="K377" t="n">
-        <v>465.708</v>
+        <v>250.878</v>
       </c>
       <c r="L377" t="s">
         <v>72</v>
@@ -16051,19 +16051,19 @@
         <v>45047</v>
       </c>
       <c r="B378" t="n">
-        <v>4.72123936005482</v>
+        <v>1.81088882161471</v>
       </c>
       <c r="C378" t="n">
-        <v>0.0244632575914809</v>
+        <v>0.131161829809274</v>
       </c>
       <c r="D378" t="n">
-        <v>0.00969713782102064</v>
+        <v>0.0297332612481716</v>
       </c>
       <c r="E378" t="n">
-        <v>55.8730685615646</v>
+        <v>62.4768648510548</v>
       </c>
       <c r="F378" t="n">
-        <v>243.265510728652</v>
+        <v>306.793415400317</v>
       </c>
       <c r="G378" t="s">
         <v>71</v>
@@ -16072,13 +16072,13 @@
         <v>6</v>
       </c>
       <c r="I378" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="J378" t="s">
         <v>53</v>
       </c>
       <c r="K378" t="n">
-        <v>0.787</v>
+        <v>0.303</v>
       </c>
       <c r="L378" t="s">
         <v>15</v>
@@ -16092,19 +16092,19 @@
         <v>45078</v>
       </c>
       <c r="B379" t="n">
-        <v>4.67520582106263</v>
+        <v>2.48149998302386</v>
       </c>
       <c r="C379" t="n">
-        <v>0.0255406395075232</v>
+        <v>0.125350988402369</v>
       </c>
       <c r="D379" t="n">
-        <v>0.00814556607557468</v>
+        <v>0.0288594659490312</v>
       </c>
       <c r="E379" t="n">
-        <v>56.7611821402991</v>
+        <v>63.879396346492</v>
       </c>
       <c r="F379" t="n">
-        <v>250.882919209588</v>
+        <v>317.388766359115</v>
       </c>
       <c r="G379" t="s">
         <v>71</v>
@@ -16113,13 +16113,13 @@
         <v>2</v>
       </c>
       <c r="I379" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J379" t="s">
         <v>14</v>
       </c>
       <c r="K379" t="n">
-        <v>2.331</v>
+        <v>1.24</v>
       </c>
       <c r="L379" t="s">
         <v>15</v>
@@ -16133,19 +16133,19 @@
         <v>45108</v>
       </c>
       <c r="B380" t="n">
-        <v>4.7175940383338</v>
+        <v>1.71999393641196</v>
       </c>
       <c r="C380" t="n">
-        <v>0.0272249254169356</v>
+        <v>0.129795015058069</v>
       </c>
       <c r="D380" t="n">
-        <v>0.00901172059591379</v>
+        <v>0.0280167077706077</v>
       </c>
       <c r="E380" t="n">
-        <v>57.6522067575323</v>
+        <v>65.3028612995855</v>
       </c>
       <c r="F380" t="n">
-        <v>258.425361728635</v>
+        <v>328.268911758968</v>
       </c>
       <c r="G380" t="s">
         <v>71</v>
@@ -16154,13 +16154,13 @@
         <v>5</v>
       </c>
       <c r="I380" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="J380" t="s">
         <v>53</v>
       </c>
       <c r="K380" t="n">
-        <v>0.944</v>
+        <v>0.345</v>
       </c>
       <c r="L380" t="s">
         <v>15</v>
@@ -16174,19 +16174,19 @@
         <v>45139</v>
       </c>
       <c r="B381" t="n">
-        <v>4.71629058325594</v>
+        <v>2.42209620520557</v>
       </c>
       <c r="C381" t="n">
-        <v>0.0222530312799766</v>
+        <v>0.13750158707886</v>
       </c>
       <c r="D381" t="n">
-        <v>0.00772661656852988</v>
+        <v>0.0272036638252212</v>
       </c>
       <c r="E381" t="n">
-        <v>58.5461672286811</v>
+        <v>66.7474932037699</v>
       </c>
       <c r="F381" t="n">
-        <v>266.470443475002</v>
+        <v>339.439951020057</v>
       </c>
       <c r="G381" t="s">
         <v>71</v>
@@ -16195,13 +16195,13 @@
         <v>4</v>
       </c>
       <c r="I381" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J381" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="K381" t="n">
-        <v>1.179</v>
+        <v>0.607</v>
       </c>
       <c r="L381" t="s">
         <v>15</v>
@@ -16215,19 +16215,19 @@
         <v>45170</v>
       </c>
       <c r="B382" t="n">
-        <v>4.70203580382629</v>
+        <v>1.7092282310326</v>
       </c>
       <c r="C382" t="n">
-        <v>0.0229429116393561</v>
+        <v>0.129803752917775</v>
       </c>
       <c r="D382" t="n">
-        <v>0.00728841682917</v>
+        <v>0.0264190781165277</v>
       </c>
       <c r="E382" t="n">
-        <v>59.4430872359974</v>
+        <v>68.2135273232825</v>
       </c>
       <c r="F382" t="n">
-        <v>274.67790755346</v>
+        <v>350.908090202237</v>
       </c>
       <c r="G382" t="s">
         <v>71</v>
@@ -16236,13 +16236,13 @@
         <v>7</v>
       </c>
       <c r="I382" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="J382" t="s">
         <v>53</v>
       </c>
       <c r="K382" t="n">
-        <v>0.672</v>
+        <v>0.245</v>
       </c>
       <c r="L382" t="s">
         <v>15</v>
@@ -16256,19 +16256,19 @@
         <v>45200</v>
       </c>
       <c r="B383" t="n">
-        <v>4.73842834534736</v>
+        <v>2.48938214545574</v>
       </c>
       <c r="C383" t="n">
-        <v>0.0216835955076759</v>
+        <v>0.132354319912579</v>
       </c>
       <c r="D383" t="n">
-        <v>0.00702650544798125</v>
+        <v>0.0256617575819014</v>
       </c>
       <c r="E383" t="n">
-        <v>60.3429894011235</v>
+        <v>69.7012007166201</v>
       </c>
       <c r="F383" t="n">
-        <v>282.85416076712</v>
+        <v>362.679643580102</v>
       </c>
       <c r="G383" t="s">
         <v>71</v>
@@ -16277,13 +16277,13 @@
         <v>4</v>
       </c>
       <c r="I383" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="J383" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="K383" t="n">
-        <v>1.184</v>
+        <v>0.623</v>
       </c>
       <c r="L383" t="s">
         <v>15</v>
@@ -16297,19 +16297,19 @@
         <v>45231</v>
       </c>
       <c r="B384" t="n">
-        <v>4.70806010048403</v>
+        <v>1.69788685657382</v>
       </c>
       <c r="C384" t="n">
-        <v>0.0214362334783667</v>
+        <v>0.118910116098481</v>
       </c>
       <c r="D384" t="n">
-        <v>0.00797568213896143</v>
+        <v>0.0249305684048631</v>
       </c>
       <c r="E384" t="n">
-        <v>61.2458953520388</v>
+        <v>71.2107522593695</v>
       </c>
       <c r="F384" t="n">
-        <v>291.401673706486</v>
+        <v>374.761035237147</v>
       </c>
       <c r="G384" t="s">
         <v>71</v>
@@ -16318,13 +16318,13 @@
         <v>7</v>
       </c>
       <c r="I384" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="J384" t="s">
         <v>53</v>
       </c>
       <c r="K384" t="n">
-        <v>0.673</v>
+        <v>0.244</v>
       </c>
       <c r="L384" t="s">
         <v>15</v>
@@ -16338,19 +16338,19 @@
         <v>45261</v>
       </c>
       <c r="B385" t="n">
-        <v>4.7440112696503</v>
+        <v>2.57021917522262</v>
       </c>
       <c r="C385" t="n">
-        <v>0.0205407238166808</v>
+        <v>0.12745886960617</v>
       </c>
       <c r="D385" t="n">
-        <v>0.00766179322036319</v>
+        <v>0.0242244325765994</v>
       </c>
       <c r="E385" t="n">
-        <v>62.151825784906</v>
+        <v>72.742422666471</v>
       </c>
       <c r="F385" t="n">
-        <v>300.195991880953</v>
+        <v>387.158800679328</v>
       </c>
       <c r="G385" t="s">
         <v>71</v>
@@ -16359,13 +16359,13 @@
         <v>3</v>
       </c>
       <c r="I385" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J385" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="K385" t="n">
-        <v>1.579</v>
+        <v>0.857</v>
       </c>
       <c r="L385" t="s">
         <v>15</v>

--- a/Outcome/Appendix/figure_data/fig9.xlsx
+++ b/Outcome/Appendix/figure_data/fig9.xlsx
@@ -14411,7 +14411,7 @@
         <v>43831</v>
       </c>
       <c r="B338" t="n">
-        <v>6.25135948094788</v>
+        <v>6.44540966026613</v>
       </c>
       <c r="C338" t="n">
         <v>0.454170338166207</v>
@@ -14438,7 +14438,7 @@
         <v>53</v>
       </c>
       <c r="K338" t="n">
-        <v>0.626</v>
+        <v>0.645</v>
       </c>
       <c r="L338" t="s">
         <v>15</v>
@@ -14452,10 +14452,10 @@
         <v>43862</v>
       </c>
       <c r="B339" t="n">
-        <v>2.11142732668997</v>
+        <v>1.45755005102892</v>
       </c>
       <c r="C339" t="n">
-        <v>0.173469203548023</v>
+        <v>0.113127888548932</v>
       </c>
       <c r="D339" t="n">
         <v>0.0686066585099932</v>
@@ -14473,13 +14473,13 @@
         <v>3</v>
       </c>
       <c r="I339" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J339" t="s">
         <v>53</v>
       </c>
       <c r="K339" t="n">
-        <v>0.705</v>
+        <v>0.488</v>
       </c>
       <c r="L339" t="s">
         <v>15</v>
@@ -14493,7 +14493,7 @@
         <v>43891</v>
       </c>
       <c r="B340" t="n">
-        <v>3.5095044974436</v>
+        <v>3.58026841651633</v>
       </c>
       <c r="C340" t="n">
         <v>0.424048155069521</v>
@@ -14520,7 +14520,7 @@
         <v>53</v>
       </c>
       <c r="K340" t="n">
-        <v>0.439</v>
+        <v>0.448</v>
       </c>
       <c r="L340" t="s">
         <v>15</v>
@@ -14534,13 +14534,13 @@
         <v>43922</v>
       </c>
       <c r="B341" t="n">
-        <v>2.77541913705538</v>
+        <v>2.40861188699422</v>
       </c>
       <c r="C341" t="n">
-        <v>0.303319360827116</v>
+        <v>0.161616683298448</v>
       </c>
       <c r="D341" t="n">
-        <v>0.100892297426241</v>
+        <v>0.0969803754503955</v>
       </c>
       <c r="E341" t="n">
         <v>25.419966274567</v>
@@ -14555,13 +14555,13 @@
         <v>2</v>
       </c>
       <c r="I341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J341" t="s">
         <v>14</v>
       </c>
       <c r="K341" t="n">
-        <v>1.386</v>
+        <v>1.203</v>
       </c>
       <c r="L341" t="s">
         <v>15</v>
@@ -14575,7 +14575,7 @@
         <v>43952</v>
       </c>
       <c r="B342" t="n">
-        <v>2.80798037644665</v>
+        <v>2.63357889060917</v>
       </c>
       <c r="C342" t="n">
         <v>0.277160888917883</v>
@@ -14602,7 +14602,7 @@
         <v>14</v>
       </c>
       <c r="K342" t="n">
-        <v>2.79</v>
+        <v>2.617</v>
       </c>
       <c r="L342" t="s">
         <v>15</v>
@@ -14616,10 +14616,10 @@
         <v>43983</v>
       </c>
       <c r="B343" t="n">
-        <v>3.2707189880719</v>
+        <v>2.66466172405097</v>
       </c>
       <c r="C343" t="n">
-        <v>0.320571440758656</v>
+        <v>0.290114489662327</v>
       </c>
       <c r="D343" t="n">
         <v>0.099277141650909</v>
@@ -14643,7 +14643,7 @@
         <v>53</v>
       </c>
       <c r="K343" t="n">
-        <v>0.818</v>
+        <v>0.667</v>
       </c>
       <c r="L343" t="s">
         <v>15</v>
@@ -14657,10 +14657,10 @@
         <v>44013</v>
       </c>
       <c r="B344" t="n">
-        <v>2.35312527164478</v>
+        <v>2.52382446068308</v>
       </c>
       <c r="C344" t="n">
-        <v>0.297858732968617</v>
+        <v>0.31222656281397</v>
       </c>
       <c r="D344" t="n">
         <v>0.095352126516606</v>
@@ -14678,13 +14678,13 @@
         <v>2</v>
       </c>
       <c r="I344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J344" t="s">
         <v>14</v>
       </c>
       <c r="K344" t="n">
-        <v>1.176</v>
+        <v>1.261</v>
       </c>
       <c r="L344" t="s">
         <v>15</v>
@@ -14698,13 +14698,13 @@
         <v>44044</v>
       </c>
       <c r="B345" t="n">
-        <v>3.16811906800544</v>
+        <v>3.01744054522517</v>
       </c>
       <c r="C345" t="n">
-        <v>0.290268971329614</v>
+        <v>0.171813896024628</v>
       </c>
       <c r="D345" t="n">
-        <v>0.0916252847338969</v>
+        <v>0.070964437261557</v>
       </c>
       <c r="E345" t="n">
         <v>28.316187242018</v>
@@ -14725,7 +14725,7 @@
         <v>53</v>
       </c>
       <c r="K345" t="n">
-        <v>0.793</v>
+        <v>0.755</v>
       </c>
       <c r="L345" t="s">
         <v>15</v>
@@ -14739,13 +14739,13 @@
         <v>44075</v>
       </c>
       <c r="B346" t="n">
-        <v>2.02298731782924</v>
+        <v>1.9152311221014</v>
       </c>
       <c r="C346" t="n">
-        <v>0.0869620598572023</v>
+        <v>0.128503685978494</v>
       </c>
       <c r="D346" t="n">
-        <v>0.0292252696984278</v>
+        <v>0.0389437391489838</v>
       </c>
       <c r="E346" t="n">
         <v>29.055459028013</v>
@@ -14766,7 +14766,7 @@
         <v>53</v>
       </c>
       <c r="K346" t="n">
-        <v>0.406</v>
+        <v>0.384</v>
       </c>
       <c r="L346" t="s">
         <v>15</v>
@@ -14780,13 +14780,13 @@
         <v>44105</v>
       </c>
       <c r="B347" t="n">
-        <v>2.84158633714708</v>
+        <v>3.12070617304442</v>
       </c>
       <c r="C347" t="n">
-        <v>0.279896135182077</v>
+        <v>0.18287856373864</v>
       </c>
       <c r="D347" t="n">
-        <v>0.0847167575749647</v>
+        <v>0.0598709670699981</v>
       </c>
       <c r="E347" t="n">
         <v>29.8054900058925</v>
@@ -14807,7 +14807,7 @@
         <v>53</v>
       </c>
       <c r="K347" t="n">
-        <v>0.711</v>
+        <v>0.781</v>
       </c>
       <c r="L347" t="s">
         <v>15</v>
@@ -14821,13 +14821,13 @@
         <v>44136</v>
       </c>
       <c r="B348" t="n">
-        <v>1.55694332693314</v>
+        <v>1.73034491877545</v>
       </c>
       <c r="C348" t="n">
-        <v>0.0513160126864068</v>
+        <v>0.0928742288654601</v>
       </c>
       <c r="D348" t="n">
-        <v>0.0195443897684454</v>
+        <v>0.0249852797621451</v>
       </c>
       <c r="E348" t="n">
         <v>30.5664083859404</v>
@@ -14848,7 +14848,7 @@
         <v>53</v>
       </c>
       <c r="K348" t="n">
-        <v>0.78</v>
+        <v>0.866</v>
       </c>
       <c r="L348" t="s">
         <v>15</v>
@@ -14862,13 +14862,13 @@
         <v>44166</v>
       </c>
       <c r="B349" t="n">
-        <v>2.57526507861285</v>
+        <v>2.81501931249439</v>
       </c>
       <c r="C349" t="n">
-        <v>0.234359639380836</v>
+        <v>0.168961965816819</v>
       </c>
       <c r="D349" t="n">
-        <v>0.0784621248039357</v>
+        <v>0.0514388604807773</v>
       </c>
       <c r="E349" t="n">
         <v>31.3383423634748</v>
@@ -14889,7 +14889,7 @@
         <v>14</v>
       </c>
       <c r="K349" t="n">
-        <v>2.56</v>
+        <v>2.797</v>
       </c>
       <c r="L349" t="s">
         <v>15</v>
@@ -14903,13 +14903,13 @@
         <v>44197</v>
       </c>
       <c r="B350" t="n">
-        <v>1.32996308569854</v>
+        <v>1.12643262765402</v>
       </c>
       <c r="C350" t="n">
-        <v>0.0348181734031333</v>
+        <v>0.0670540104974328</v>
       </c>
       <c r="D350" t="n">
-        <v>0.0134114264470131</v>
+        <v>0.0265620492182988</v>
       </c>
       <c r="E350" t="n">
         <v>32.1214201984579</v>
@@ -14930,7 +14930,7 @@
         <v>53</v>
       </c>
       <c r="K350" t="n">
-        <v>0.667</v>
+        <v>0.565</v>
       </c>
       <c r="L350" t="s">
         <v>15</v>
@@ -14944,10 +14944,10 @@
         <v>44228</v>
       </c>
       <c r="B351" t="n">
-        <v>2.20200266938457</v>
+        <v>2.33441482133965</v>
       </c>
       <c r="C351" t="n">
-        <v>0.234031850708107</v>
+        <v>0.180566701136524</v>
       </c>
       <c r="D351" t="n">
         <v>0.0727849688791691</v>
@@ -14971,7 +14971,7 @@
         <v>53</v>
       </c>
       <c r="K351" t="n">
-        <v>0.735</v>
+        <v>0.779</v>
       </c>
       <c r="L351" t="s">
         <v>15</v>
@@ -14985,13 +14985,13 @@
         <v>44256</v>
       </c>
       <c r="B352" t="n">
-        <v>1.56358551194237</v>
+        <v>1.07895849024305</v>
       </c>
       <c r="C352" t="n">
-        <v>0.0473611284058548</v>
+        <v>0.0708553677060055</v>
       </c>
       <c r="D352" t="n">
-        <v>0.02092014457375</v>
+        <v>0.0319908085946911</v>
       </c>
       <c r="E352" t="n">
         <v>33.7215212313925</v>
@@ -15006,13 +15006,13 @@
         <v>6</v>
       </c>
       <c r="I352" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J352" t="s">
         <v>53</v>
       </c>
       <c r="K352" t="n">
-        <v>0.262</v>
+        <v>0.181</v>
       </c>
       <c r="L352" t="s">
         <v>15</v>
@@ -15026,13 +15026,13 @@
         <v>44287</v>
       </c>
       <c r="B353" t="n">
-        <v>2.71090612649237</v>
+        <v>2.30454898585209</v>
       </c>
       <c r="C353" t="n">
-        <v>0.162640306269854</v>
+        <v>0.196444748451376</v>
       </c>
       <c r="D353" t="n">
-        <v>0.0655781608080556</v>
+        <v>0.0676196541735899</v>
       </c>
       <c r="E353" t="n">
         <v>34.5388018920301</v>
@@ -15047,13 +15047,13 @@
         <v>5</v>
       </c>
       <c r="I353" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J353" t="s">
         <v>53</v>
       </c>
       <c r="K353" t="n">
-        <v>0.543</v>
+        <v>0.462</v>
       </c>
       <c r="L353" t="s">
         <v>15</v>
@@ -15067,13 +15067,13 @@
         <v>44317</v>
       </c>
       <c r="B354" t="n">
-        <v>1.46975268365974</v>
+        <v>1.11153853255968</v>
       </c>
       <c r="C354" t="n">
-        <v>0.0553199434733969</v>
+        <v>0.0925507912725509</v>
       </c>
       <c r="D354" t="n">
-        <v>0.0268298658838945</v>
+        <v>0.0310207642816756</v>
       </c>
       <c r="E354" t="n">
         <v>35.3677414508137</v>
@@ -15094,7 +15094,7 @@
         <v>14</v>
       </c>
       <c r="K354" t="n">
-        <v>1.465</v>
+        <v>1.11</v>
       </c>
       <c r="L354" t="s">
         <v>15</v>
@@ -15108,13 +15108,13 @@
         <v>44348</v>
       </c>
       <c r="B355" t="n">
-        <v>2.71013522774545</v>
+        <v>2.65031166340173</v>
       </c>
       <c r="C355" t="n">
-        <v>0.117731805302578</v>
+        <v>0.206157276120681</v>
       </c>
       <c r="D355" t="n">
-        <v>0.0364300369926969</v>
+        <v>0.0629095338394639</v>
       </c>
       <c r="E355" t="n">
         <v>36.2084694576365</v>
@@ -15135,7 +15135,7 @@
         <v>53</v>
       </c>
       <c r="K355" t="n">
-        <v>0.678</v>
+        <v>0.663</v>
       </c>
       <c r="L355" t="s">
         <v>15</v>
@@ -15149,13 +15149,13 @@
         <v>44378</v>
       </c>
       <c r="B356" t="n">
-        <v>1.95197393742874</v>
+        <v>1.39729494115526</v>
       </c>
       <c r="C356" t="n">
-        <v>0.105889547849657</v>
+        <v>0.152368387145571</v>
       </c>
       <c r="D356" t="n">
-        <v>0.0426556049675676</v>
+        <v>0.0524539991800067</v>
       </c>
       <c r="E356" t="n">
         <v>37.0611158778131</v>
@@ -15170,13 +15170,13 @@
         <v>3</v>
       </c>
       <c r="I356" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J356" t="s">
         <v>53</v>
       </c>
       <c r="K356" t="n">
-        <v>0.652</v>
+        <v>0.468</v>
       </c>
       <c r="L356" t="s">
         <v>15</v>
@@ -15190,13 +15190,13 @@
         <v>44409</v>
       </c>
       <c r="B357" t="n">
-        <v>2.28910124267079</v>
+        <v>2.26519696865582</v>
       </c>
       <c r="C357" t="n">
-        <v>0.0931332972542656</v>
+        <v>0.186150553036016</v>
       </c>
       <c r="D357" t="n">
-        <v>0.0266324612941225</v>
+        <v>0.058605500371825</v>
       </c>
       <c r="E357" t="n">
         <v>37.9258111350872</v>
@@ -15217,7 +15217,7 @@
         <v>14</v>
       </c>
       <c r="K357" t="n">
-        <v>1.144</v>
+        <v>1.132</v>
       </c>
       <c r="L357" t="s">
         <v>15</v>
@@ -15231,10 +15231,10 @@
         <v>44440</v>
       </c>
       <c r="B358" t="n">
-        <v>1.976892008557</v>
+        <v>1.98108032778872</v>
       </c>
       <c r="C358" t="n">
-        <v>0.114693950951088</v>
+        <v>0.17767124771887</v>
       </c>
       <c r="D358" t="n">
         <v>0.0565921866525776</v>
@@ -15258,7 +15258,7 @@
         <v>14</v>
       </c>
       <c r="K358" t="n">
-        <v>1.967</v>
+        <v>1.971</v>
       </c>
       <c r="L358" t="s">
         <v>15</v>
@@ -15272,13 +15272,13 @@
         <v>44470</v>
       </c>
       <c r="B359" t="n">
-        <v>2.74747972108207</v>
+        <v>2.24952469341971</v>
       </c>
       <c r="C359" t="n">
-        <v>0.124118072311289</v>
+        <v>0.169521576526433</v>
       </c>
       <c r="D359" t="n">
-        <v>0.0437580796917787</v>
+        <v>0.054664805423579</v>
       </c>
       <c r="E359" t="n">
         <v>39.6918723839059</v>
@@ -15293,13 +15293,13 @@
         <v>1</v>
       </c>
       <c r="I359" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J359" t="s">
         <v>14</v>
       </c>
       <c r="K359" t="n">
-        <v>2.73</v>
+        <v>2.237</v>
       </c>
       <c r="L359" t="s">
         <v>15</v>
@@ -15313,13 +15313,13 @@
         <v>44501</v>
       </c>
       <c r="B360" t="n">
-        <v>1.93171130807709</v>
+        <v>2.12130811613357</v>
       </c>
       <c r="C360" t="n">
-        <v>0.110598341451956</v>
+        <v>0.175557419434896</v>
       </c>
       <c r="D360" t="n">
-        <v>0.0503682883066684</v>
+        <v>0.0528188481503957</v>
       </c>
       <c r="E360" t="n">
         <v>40.5935018590583</v>
@@ -15337,10 +15337,10 @@
         <v>0</v>
       </c>
       <c r="J360" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="K360" t="n">
-        <v>0.966</v>
+        <v>1.06</v>
       </c>
       <c r="L360" t="s">
         <v>15</v>
@@ -15354,13 +15354,13 @@
         <v>44531</v>
       </c>
       <c r="B361" t="n">
-        <v>2.41019494918812</v>
+        <v>2.07311179769219</v>
       </c>
       <c r="C361" t="n">
-        <v>0.112757574346345</v>
+        <v>0.162683774074849</v>
       </c>
       <c r="D361" t="n">
-        <v>0.044256076116868</v>
+        <v>0.0510500923484152</v>
       </c>
       <c r="E361" t="n">
         <v>41.6184294676252</v>
@@ -15381,7 +15381,7 @@
         <v>53</v>
       </c>
       <c r="K361" t="n">
-        <v>0.804</v>
+        <v>0.692</v>
       </c>
       <c r="L361" t="s">
         <v>15</v>
@@ -15395,10 +15395,10 @@
         <v>44562</v>
       </c>
       <c r="B362" t="n">
-        <v>1.73449173937269</v>
+        <v>1.70840206766541</v>
       </c>
       <c r="C362" t="n">
-        <v>0.0992461894323059</v>
+        <v>0.165431577825995</v>
       </c>
       <c r="D362" t="n">
         <v>0.049354580046809</v>
@@ -15422,7 +15422,7 @@
         <v>53</v>
       </c>
       <c r="K362" t="n">
-        <v>0.29</v>
+        <v>0.286</v>
       </c>
       <c r="L362" t="s">
         <v>15</v>
@@ -15436,10 +15436,10 @@
         <v>44593</v>
       </c>
       <c r="B363" t="n">
-        <v>2.09349535047082</v>
+        <v>1.90292054266747</v>
       </c>
       <c r="C363" t="n">
-        <v>0.139694120963703</v>
+        <v>0.189238463580228</v>
       </c>
       <c r="D363" t="n">
         <v>0.0477285981404548</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="J363" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="K363" t="n">
-        <v>1.047</v>
+        <v>0.952</v>
       </c>
       <c r="L363" t="s">
         <v>15</v>
@@ -15477,13 +15477,13 @@
         <v>44621</v>
       </c>
       <c r="B364" t="n">
-        <v>1.67215366365178</v>
+        <v>1.48729431293768</v>
       </c>
       <c r="C364" t="n">
-        <v>0.0913604930729469</v>
+        <v>0.166750534976894</v>
       </c>
       <c r="D364" t="n">
-        <v>0.0373174604537924</v>
+        <v>0.0461686604404346</v>
       </c>
       <c r="E364" t="n">
         <v>44.9126713622174</v>
@@ -15498,13 +15498,13 @@
         <v>4</v>
       </c>
       <c r="I364" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J364" t="s">
         <v>53</v>
       </c>
       <c r="K364" t="n">
-        <v>0.419</v>
+        <v>0.373</v>
       </c>
       <c r="L364" t="s">
         <v>15</v>
@@ -15518,10 +15518,10 @@
         <v>44652</v>
       </c>
       <c r="B365" t="n">
-        <v>2.59599784778565</v>
+        <v>2.40408245083686</v>
       </c>
       <c r="C365" t="n">
-        <v>0.134869150412994</v>
+        <v>0.184359998386413</v>
       </c>
       <c r="D365" t="n">
         <v>0.0446714912551257</v>
@@ -15539,13 +15539,13 @@
         <v>1</v>
       </c>
       <c r="I365" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J365" t="s">
         <v>14</v>
       </c>
       <c r="K365" t="n">
-        <v>2.58</v>
+        <v>2.39</v>
       </c>
       <c r="L365" t="s">
         <v>15</v>
@@ -15559,10 +15559,10 @@
         <v>44682</v>
       </c>
       <c r="B366" t="n">
-        <v>1.95563575668386</v>
+        <v>1.59931876161351</v>
       </c>
       <c r="C366" t="n">
-        <v>0.101600390828041</v>
+        <v>0.165595229131481</v>
       </c>
       <c r="D366" t="n">
         <v>0.0432340103526227</v>
@@ -15586,7 +15586,7 @@
         <v>53</v>
       </c>
       <c r="K366" t="n">
-        <v>0.49</v>
+        <v>0.401</v>
       </c>
       <c r="L366" t="s">
         <v>15</v>
@@ -15600,10 +15600,10 @@
         <v>44713</v>
       </c>
       <c r="B367" t="n">
-        <v>2.48562591701092</v>
+        <v>2.41074818197813</v>
       </c>
       <c r="C367" t="n">
-        <v>0.135644833532041</v>
+        <v>0.181479258933914</v>
       </c>
       <c r="D367" t="n">
         <v>0.0418533191716252</v>
@@ -15627,7 +15627,7 @@
         <v>53</v>
       </c>
       <c r="K367" t="n">
-        <v>0.829</v>
+        <v>0.804</v>
       </c>
       <c r="L367" t="s">
         <v>15</v>
@@ -15641,10 +15641,10 @@
         <v>44743</v>
       </c>
       <c r="B368" t="n">
-        <v>1.96564782678572</v>
+        <v>1.88786066971801</v>
       </c>
       <c r="C368" t="n">
-        <v>0.124701900676866</v>
+        <v>0.174041971103253</v>
       </c>
       <c r="D368" t="n">
         <v>0.0405266881623213</v>
@@ -15668,7 +15668,7 @@
         <v>53</v>
       </c>
       <c r="K368" t="n">
-        <v>0.219</v>
+        <v>0.211</v>
       </c>
       <c r="L368" t="s">
         <v>15</v>
@@ -15682,10 +15682,10 @@
         <v>44774</v>
       </c>
       <c r="B369" t="n">
-        <v>2.42839404899964</v>
+        <v>2.37378056558492</v>
       </c>
       <c r="C369" t="n">
-        <v>0.135828541904854</v>
+        <v>0.174752014985918</v>
       </c>
       <c r="D369" t="n">
         <v>0.039251545151455</v>
@@ -15709,7 +15709,7 @@
         <v>53</v>
       </c>
       <c r="K369" t="n">
-        <v>0.348</v>
+        <v>0.34</v>
       </c>
       <c r="L369" t="s">
         <v>15</v>
@@ -15723,10 +15723,10 @@
         <v>44805</v>
       </c>
       <c r="B370" t="n">
-        <v>1.78901327916856</v>
+        <v>1.98710514436367</v>
       </c>
       <c r="C370" t="n">
-        <v>0.118885304640667</v>
+        <v>0.170583034401326</v>
       </c>
       <c r="D370" t="n">
         <v>0.0380254646369259</v>
@@ -15750,7 +15750,7 @@
         <v>14</v>
       </c>
       <c r="K370" t="n">
-        <v>179.901</v>
+        <v>199.711</v>
       </c>
       <c r="L370" t="s">
         <v>72</v>
@@ -15764,10 +15764,10 @@
         <v>44835</v>
       </c>
       <c r="B371" t="n">
-        <v>2.35364126001695</v>
+        <v>2.12634790046077</v>
       </c>
       <c r="C371" t="n">
-        <v>0.14528816089829</v>
+        <v>0.167673368471301</v>
       </c>
       <c r="D371" t="n">
         <v>0.036846157927115</v>
@@ -15791,7 +15791,7 @@
         <v>14</v>
       </c>
       <c r="K371" t="n">
-        <v>1.176</v>
+        <v>1.063</v>
       </c>
       <c r="L371" t="s">
         <v>15</v>
@@ -15805,10 +15805,10 @@
         <v>44866</v>
       </c>
       <c r="B372" t="n">
-        <v>1.72595728625882</v>
+        <v>1.96698928906729</v>
       </c>
       <c r="C372" t="n">
-        <v>0.114310372799973</v>
+        <v>0.164278839678332</v>
       </c>
       <c r="D372" t="n">
         <v>0.0357114640488407</v>
@@ -15832,7 +15832,7 @@
         <v>53</v>
       </c>
       <c r="K372" t="n">
-        <v>0.577</v>
+        <v>0.657</v>
       </c>
       <c r="L372" t="s">
         <v>15</v>
@@ -15846,10 +15846,10 @@
         <v>44896</v>
       </c>
       <c r="B373" t="n">
-        <v>2.43417602347705</v>
+        <v>1.95197783849961</v>
       </c>
       <c r="C373" t="n">
-        <v>0.144373229974249</v>
+        <v>0.160976225144882</v>
       </c>
       <c r="D373" t="n">
         <v>0.0346193413555652</v>
@@ -15870,10 +15870,10 @@
         <v>0</v>
       </c>
       <c r="J373" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="K373" t="n">
-        <v>1.216</v>
+        <v>0.976</v>
       </c>
       <c r="L373" t="s">
         <v>15</v>
@@ -15887,10 +15887,10 @@
         <v>44927</v>
       </c>
       <c r="B374" t="n">
-        <v>1.83020977210463</v>
+        <v>1.77990120825641</v>
       </c>
       <c r="C374" t="n">
-        <v>0.117656381702524</v>
+        <v>0.15776226110437</v>
       </c>
       <c r="D374" t="n">
         <v>0.0335678597743147</v>
@@ -15914,7 +15914,7 @@
         <v>53</v>
       </c>
       <c r="K374" t="n">
-        <v>0.167</v>
+        <v>0.163</v>
       </c>
       <c r="L374" t="s">
         <v>15</v>
@@ -15928,10 +15928,10 @@
         <v>44958</v>
       </c>
       <c r="B375" t="n">
-        <v>2.51253625879777</v>
+        <v>2.14120723778098</v>
       </c>
       <c r="C375" t="n">
-        <v>0.134316264629236</v>
+        <v>0.154633831302699</v>
       </c>
       <c r="D375" t="n">
         <v>0.0325551936358638</v>
@@ -15949,13 +15949,13 @@
         <v>6</v>
       </c>
       <c r="I375" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J375" t="s">
         <v>53</v>
       </c>
       <c r="K375" t="n">
-        <v>0.42</v>
+        <v>0.358</v>
       </c>
       <c r="L375" t="s">
         <v>15</v>
@@ -15969,10 +15969,10 @@
         <v>44986</v>
       </c>
       <c r="B376" t="n">
-        <v>1.84116075256485</v>
+        <v>1.56457633862883</v>
       </c>
       <c r="C376" t="n">
-        <v>0.120243706176178</v>
+        <v>0.15158795878048</v>
       </c>
       <c r="D376" t="n">
         <v>0.0315796150381476</v>
@@ -15996,7 +15996,7 @@
         <v>53</v>
       </c>
       <c r="K376" t="n">
-        <v>0.264</v>
+        <v>0.225</v>
       </c>
       <c r="L376" t="s">
         <v>15</v>
@@ -16010,10 +16010,10 @@
         <v>45017</v>
       </c>
       <c r="B377" t="n">
-        <v>2.49878496440025</v>
+        <v>2.30071365803141</v>
       </c>
       <c r="C377" t="n">
-        <v>0.142119852229573</v>
+        <v>0.14862179820314</v>
       </c>
       <c r="D377" t="n">
         <v>0.0306394876976929</v>
@@ -16037,7 +16037,7 @@
         <v>14</v>
       </c>
       <c r="K377" t="n">
-        <v>250.878</v>
+        <v>231.071</v>
       </c>
       <c r="L377" t="s">
         <v>72</v>
@@ -16051,10 +16051,10 @@
         <v>45047</v>
       </c>
       <c r="B378" t="n">
-        <v>1.81088882161471</v>
+        <v>1.78148008341785</v>
       </c>
       <c r="C378" t="n">
-        <v>0.131161829809274</v>
+        <v>0.145732628696283</v>
       </c>
       <c r="D378" t="n">
         <v>0.0297332612481716</v>
@@ -16078,7 +16078,7 @@
         <v>53</v>
       </c>
       <c r="K378" t="n">
-        <v>0.303</v>
+        <v>0.298</v>
       </c>
       <c r="L378" t="s">
         <v>15</v>
@@ -16092,10 +16092,10 @@
         <v>45078</v>
       </c>
       <c r="B379" t="n">
-        <v>2.48149998302386</v>
+        <v>2.12866778689126</v>
       </c>
       <c r="C379" t="n">
-        <v>0.125350988402369</v>
+        <v>0.142917847147453</v>
       </c>
       <c r="D379" t="n">
         <v>0.0288594659490312</v>
@@ -16119,7 +16119,7 @@
         <v>14</v>
       </c>
       <c r="K379" t="n">
-        <v>1.24</v>
+        <v>1.064</v>
       </c>
       <c r="L379" t="s">
         <v>15</v>
@@ -16133,10 +16133,10 @@
         <v>45108</v>
       </c>
       <c r="B380" t="n">
-        <v>1.71999393641196</v>
+        <v>1.66319713944643</v>
       </c>
       <c r="C380" t="n">
-        <v>0.129795015058069</v>
+        <v>0.14017496193888</v>
       </c>
       <c r="D380" t="n">
         <v>0.0280167077706077</v>
@@ -16160,7 +16160,7 @@
         <v>53</v>
       </c>
       <c r="K380" t="n">
-        <v>0.345</v>
+        <v>0.334</v>
       </c>
       <c r="L380" t="s">
         <v>15</v>
@@ -16174,7 +16174,7 @@
         <v>45139</v>
       </c>
       <c r="B381" t="n">
-        <v>2.42209620520557</v>
+        <v>2.11601362929082</v>
       </c>
       <c r="C381" t="n">
         <v>0.13750158707886</v>
@@ -16201,7 +16201,7 @@
         <v>53</v>
       </c>
       <c r="K381" t="n">
-        <v>0.607</v>
+        <v>0.53</v>
       </c>
       <c r="L381" t="s">
         <v>15</v>
@@ -16215,10 +16215,10 @@
         <v>45170</v>
       </c>
       <c r="B382" t="n">
-        <v>1.7092282310326</v>
+        <v>1.75439485888834</v>
       </c>
       <c r="C382" t="n">
-        <v>0.129803752917775</v>
+        <v>0.134895436702188</v>
       </c>
       <c r="D382" t="n">
         <v>0.0264190781165277</v>
@@ -16242,7 +16242,7 @@
         <v>53</v>
       </c>
       <c r="K382" t="n">
-        <v>0.245</v>
+        <v>0.252</v>
       </c>
       <c r="L382" t="s">
         <v>15</v>
@@ -16256,7 +16256,7 @@
         <v>45200</v>
       </c>
       <c r="B383" t="n">
-        <v>2.48938214545574</v>
+        <v>2.10425506002624</v>
       </c>
       <c r="C383" t="n">
         <v>0.132354319912579</v>
@@ -16283,7 +16283,7 @@
         <v>53</v>
       </c>
       <c r="K383" t="n">
-        <v>0.623</v>
+        <v>0.527</v>
       </c>
       <c r="L383" t="s">
         <v>15</v>
@@ -16297,10 +16297,10 @@
         <v>45231</v>
       </c>
       <c r="B384" t="n">
-        <v>1.69788685657382</v>
+        <v>1.82362351241192</v>
       </c>
       <c r="C384" t="n">
-        <v>0.118910116098481</v>
+        <v>0.129876135942286</v>
       </c>
       <c r="D384" t="n">
         <v>0.0249305684048631</v>
@@ -16324,7 +16324,7 @@
         <v>53</v>
       </c>
       <c r="K384" t="n">
-        <v>0.244</v>
+        <v>0.262</v>
       </c>
       <c r="L384" t="s">
         <v>15</v>
@@ -16338,7 +16338,7 @@
         <v>45261</v>
       </c>
       <c r="B385" t="n">
-        <v>2.57021917522262</v>
+        <v>2.11668410566235</v>
       </c>
       <c r="C385" t="n">
         <v>0.12745886960617</v>
@@ -16359,13 +16359,13 @@
         <v>3</v>
       </c>
       <c r="I385" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J385" t="s">
         <v>53</v>
       </c>
       <c r="K385" t="n">
-        <v>0.857</v>
+        <v>0.707</v>
       </c>
       <c r="L385" t="s">
         <v>15</v>
